--- a/Element/Element.xlsx
+++ b/Element/Element.xlsx
@@ -1052,7 +1052,7 @@
         <v>5</v>
       </c>
       <c r="P4" s="9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="Q4" s="9">
         <v>320</v>
